--- a/scd2-test-case.xlsx
+++ b/scd2-test-case.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guido.schmutz/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guido.schmutz/Documents/GitHub/gschmutz/iceberg-poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8827385-B28D-AC48-AB24-B8ABF521B25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99ECE267-52D6-D443-B133-79E8BEAA0934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34260" windowHeight="21580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34260" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario-1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="90">
   <si>
     <t>ID</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>4b68df79-2c5e-4637-a0f6-6b5521e14dbe</t>
+  </si>
+  <si>
+    <t>Batch-6</t>
   </si>
 </sst>
 </file>
@@ -367,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -388,6 +391,7 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,7 +1073,7 @@
       <c r="E8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G8" t="s">
@@ -1279,7 +1283,7 @@
       <c r="E11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="12" t="s">
         <v>24</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1663,7 +1667,7 @@
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -2271,10 +2275,10 @@
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>30</v>
@@ -2502,7 +2506,7 @@
         <v>13</v>
       </c>
       <c r="O34" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P34" t="s">
         <v>15</v>
@@ -2975,7 +2979,7 @@
         <v>9</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
         <v>30</v>
@@ -3113,8 +3117,8 @@
       <c r="E47" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>29</v>
+      <c r="F47" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>11</v>
@@ -3203,7 +3207,7 @@
         <v>13</v>
       </c>
       <c r="O48" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P48" t="s">
         <v>15</v>
@@ -4166,7 +4170,7 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G11" t="s">
@@ -4264,7 +4268,7 @@
       <c r="Q12" s="5">
         <v>45658</v>
       </c>
-      <c r="R12" t="s">
+      <c r="R12" s="3" t="s">
         <v>75</v>
       </c>
       <c r="S12" t="b">
@@ -4326,7 +4330,7 @@
       <c r="O13" t="s">
         <v>18</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q13" s="5">
@@ -5987,7 +5991,7 @@
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="B47">
         <v>3</v>
